--- a/subspaces/01-academic-training/gpa-academic-standing-agent/agent/QA.xlsx
+++ b/subspaces/01-academic-training/gpa-academic-standing-agent/agent/QA.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
